--- a/src/main/resources/static/피부_재고전체파일.xlsx
+++ b/src/main/resources/static/피부_재고전체파일.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5CF5D0-E661-46D9-95EA-16277EA02A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95FB9F5-59DC-4A09-8E2B-4E52A2EC5995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-225" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025-12" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="109">
   <si>
     <t>2026-01 피부 물품(보고용)</t>
   </si>
@@ -543,16 +543,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -903,17 +903,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1234,7 +1234,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
@@ -1257,7 +1257,7 @@
         <v>29</v>
       </c>
       <c r="C14" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="3">
         <v>0</v>
@@ -1340,13 +1340,13 @@
         <v>36</v>
       </c>
       <c r="C17" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
       </c>
       <c r="E17" s="6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F17" s="3">
         <v>10</v>
@@ -1429,7 +1429,7 @@
         <v>85</v>
       </c>
       <c r="E20" s="6">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>46</v>
       </c>
       <c r="C22" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E22" s="6">
         <v>19</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2076,13 +2076,13 @@
         <v>76</v>
       </c>
       <c r="C43" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F44" s="3">
         <v>0</v>
@@ -2186,13 +2186,13 @@
         <v>82</v>
       </c>
       <c r="C47" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D47" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F47" s="3">
         <v>3</v>
@@ -2215,13 +2215,13 @@
         <v>84</v>
       </c>
       <c r="C48" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D48" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="3">
         <v>3</v>
@@ -2244,10 +2244,11 @@
         <v>86</v>
       </c>
       <c r="C49" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D49" s="3">
-        <v>56</v>
+        <f>C49-E49</f>
+        <v>14</v>
       </c>
       <c r="E49" s="6">
         <v>986</v>
@@ -2422,7 +2423,7 @@
         <v>26</v>
       </c>
       <c r="E55" s="6">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F55" s="3">
         <v>0</v>
@@ -2475,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="6">
         <v>1</v>
@@ -2531,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="D59" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="6">
         <v>1</v>
@@ -2572,17 +2573,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2624,11 +2625,11 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>0</v>
+        <f>C3-E3</f>
+        <v>1</v>
       </c>
       <c r="E3" s="6">
-        <f>C3-D3</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
@@ -2654,11 +2655,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="3">
-        <v>0</v>
+        <f t="shared" ref="D4:D59" si="0">C4-E4</f>
+        <v>1</v>
       </c>
       <c r="E4" s="6">
-        <f t="shared" ref="E4:E59" si="0">C4-D4</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3">
         <v>0</v>
@@ -2684,16 +2685,16 @@
         <v>1</v>
       </c>
       <c r="D5" s="3">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E5" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3">
         <v>0</v>
       </c>
-      <c r="G5" s="9"/>
+      <c r="G5" s="7"/>
       <c r="H5" s="2" t="s">
         <v>14</v>
       </c>
@@ -2709,19 +2710,19 @@
         <v>15</v>
       </c>
       <c r="C6" s="3">
+        <v>70</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E6" s="6">
         <v>69</v>
       </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <f t="shared" si="0"/>
-        <v>69</v>
-      </c>
       <c r="F6" s="3">
         <v>0</v>
       </c>
-      <c r="G6" s="9"/>
+      <c r="G6" s="7"/>
       <c r="H6" s="2" t="s">
         <v>16</v>
       </c>
@@ -2740,16 +2741,16 @@
         <v>1</v>
       </c>
       <c r="D7" s="3">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E7" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
       </c>
-      <c r="G7" s="9"/>
+      <c r="G7" s="7"/>
       <c r="H7" s="2" t="s">
         <v>18</v>
       </c>
@@ -2768,16 +2769,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="3">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E8" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
-      <c r="G8" s="9"/>
+      <c r="G8" s="7"/>
       <c r="H8" s="2" t="s">
         <v>20</v>
       </c>
@@ -2796,16 +2797,16 @@
         <v>1</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E9" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="9"/>
+      <c r="G9" s="7"/>
       <c r="H9" s="2" t="s">
         <v>22</v>
       </c>
@@ -2824,16 +2825,16 @@
         <v>1</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E10" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="G10" s="9"/>
+      <c r="G10" s="7"/>
       <c r="H10" s="2" t="s">
         <v>24</v>
       </c>
@@ -2852,16 +2853,16 @@
         <v>1</v>
       </c>
       <c r="D11" s="3">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E11" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="3">
         <v>0</v>
       </c>
-      <c r="G11" s="9"/>
+      <c r="G11" s="7"/>
       <c r="H11" s="2" t="s">
         <v>26</v>
       </c>
@@ -2880,11 +2881,11 @@
         <v>2</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E12" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -2910,11 +2911,11 @@
         <v>2</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E13" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
@@ -2937,19 +2938,19 @@
         <v>29</v>
       </c>
       <c r="C14" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D14" s="3">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="E14" s="6">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="9"/>
+      <c r="G14" s="7"/>
       <c r="H14" s="2" t="s">
         <v>30</v>
       </c>
@@ -2968,16 +2969,16 @@
         <v>3</v>
       </c>
       <c r="D15" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E15" s="6">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F15" s="3">
         <v>3</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="7">
         <v>46024</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -2995,19 +2996,19 @@
         <v>34</v>
       </c>
       <c r="C16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="3">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E16" s="6">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="7">
         <v>46024</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -3025,19 +3026,19 @@
         <v>36</v>
       </c>
       <c r="C17" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" s="3">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E17" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F17" s="3">
         <v>0</v>
       </c>
-      <c r="G17" s="9"/>
+      <c r="G17" s="7"/>
       <c r="H17" s="2" t="s">
         <v>37</v>
       </c>
@@ -3053,19 +3054,19 @@
         <v>38</v>
       </c>
       <c r="C18" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="3">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="E18" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="3">
         <v>2</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="7">
         <v>46024</v>
       </c>
       <c r="H18" s="2" t="s">
@@ -3083,19 +3084,19 @@
         <v>41</v>
       </c>
       <c r="C19" s="3">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E19" s="6">
         <v>4</v>
-      </c>
-      <c r="D19" s="3">
-        <v>3</v>
-      </c>
-      <c r="E19" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
       </c>
       <c r="F19" s="3">
         <v>4</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="7">
         <v>46027</v>
       </c>
       <c r="H19" s="2" t="s">
@@ -3116,16 +3117,16 @@
         <v>159</v>
       </c>
       <c r="D20" s="3">
-        <v>48</v>
+        <f t="shared" si="0"/>
+        <v>73</v>
       </c>
       <c r="E20" s="6">
-        <f t="shared" si="0"/>
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="7">
         <v>46024</v>
       </c>
       <c r="H20" s="2" t="s">
@@ -3143,14 +3144,14 @@
         <v>45</v>
       </c>
       <c r="C21" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
+      </c>
+      <c r="E21" s="6">
+        <v>3</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
@@ -3173,19 +3174,19 @@
         <v>46</v>
       </c>
       <c r="C22" s="3">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D22" s="3">
-        <v>34</v>
+        <f t="shared" si="0"/>
+        <v>55</v>
       </c>
       <c r="E22" s="6">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F22" s="3">
         <v>60</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="7">
         <v>46024</v>
       </c>
       <c r="H22" s="2" t="s">
@@ -3203,19 +3204,19 @@
         <v>49</v>
       </c>
       <c r="C23" s="3">
+        <v>8</v>
+      </c>
+      <c r="D23" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E23" s="6">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3">
         <v>5</v>
       </c>
-      <c r="D23" s="3">
-        <v>3</v>
-      </c>
-      <c r="E23" s="6">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="F23" s="3">
-        <v>80</v>
-      </c>
-      <c r="G23" s="9">
+      <c r="G23" s="7">
         <v>46027</v>
       </c>
       <c r="H23" s="2" t="s">
@@ -3233,19 +3234,19 @@
         <v>51</v>
       </c>
       <c r="C24" s="3">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D24" s="3">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="E24" s="6">
-        <f t="shared" si="0"/>
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>5</v>
-      </c>
-      <c r="G24" s="9">
+        <v>20</v>
+      </c>
+      <c r="G24" s="7">
         <v>46027</v>
       </c>
       <c r="H24" s="2" t="s">
@@ -3263,19 +3264,19 @@
         <v>53</v>
       </c>
       <c r="C25" s="3">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="D25" s="3">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>49</v>
       </c>
       <c r="E25" s="6">
-        <f t="shared" si="0"/>
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="F25" s="3">
-        <v>15</v>
-      </c>
-      <c r="G25" s="9">
+        <v>80</v>
+      </c>
+      <c r="G25" s="7">
         <v>46027</v>
       </c>
       <c r="H25" s="2" t="s">
@@ -3296,10 +3297,10 @@
         <v>2</v>
       </c>
       <c r="D26" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E26" s="6">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F26" s="3">
@@ -3323,14 +3324,14 @@
         <v>55</v>
       </c>
       <c r="C27" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E27" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
@@ -3353,14 +3354,14 @@
         <v>56</v>
       </c>
       <c r="C28" s="3">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D28" s="3">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="E28" s="6">
-        <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F28" s="3">
         <v>0</v>
@@ -3386,10 +3387,10 @@
         <v>4</v>
       </c>
       <c r="D29" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E29" s="6">
-        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F29" s="3">
@@ -3413,19 +3414,19 @@
         <v>58</v>
       </c>
       <c r="C30" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" s="3">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E30" s="6">
-        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F30" s="3">
         <v>4</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="7">
         <v>46027</v>
       </c>
       <c r="H30" s="2" t="s">
@@ -3443,19 +3444,19 @@
         <v>60</v>
       </c>
       <c r="C31" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D31" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E31" s="6">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F31" s="3">
         <v>4</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="7">
         <v>46027</v>
       </c>
       <c r="H31" s="2" t="s">
@@ -3473,19 +3474,19 @@
         <v>61</v>
       </c>
       <c r="C32" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="E32" s="6">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F32" s="3">
         <v>20</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="7">
         <v>46024</v>
       </c>
       <c r="H32" s="2" t="s">
@@ -3506,10 +3507,10 @@
         <v>9</v>
       </c>
       <c r="D33" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E33" s="6">
-        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="F33" s="3">
@@ -3533,13 +3534,13 @@
         <v>65</v>
       </c>
       <c r="C34" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D34" s="3">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E34" s="6">
-        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="F34" s="3">
@@ -3566,10 +3567,10 @@
         <v>6</v>
       </c>
       <c r="D35" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E35" s="6">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F35" s="3">
@@ -3596,10 +3597,10 @@
         <v>10</v>
       </c>
       <c r="D36" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E36" s="6">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="F36" s="3">
@@ -3626,10 +3627,10 @@
         <v>10</v>
       </c>
       <c r="D37" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E37" s="6">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="F37" s="3">
@@ -3656,10 +3657,10 @@
         <v>10</v>
       </c>
       <c r="D38" s="3">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="E38" s="6">
-        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="F38" s="3">
@@ -3683,19 +3684,19 @@
         <v>70</v>
       </c>
       <c r="C39" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D39" s="3">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="E39" s="6">
-        <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F39" s="3">
         <v>4</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="7">
         <v>46024</v>
       </c>
       <c r="H39" s="2" t="s">
@@ -3713,19 +3714,19 @@
         <v>72</v>
       </c>
       <c r="C40" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D40" s="3">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="E40" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="3">
         <v>6</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="7">
         <v>46024</v>
       </c>
       <c r="H40" s="2" t="s">
@@ -3743,19 +3744,19 @@
         <v>73</v>
       </c>
       <c r="C41" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" s="3">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="E41" s="6">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F41" s="3">
         <v>7</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="7">
         <v>46024</v>
       </c>
       <c r="H41" s="2" t="s">
@@ -3776,11 +3777,11 @@
         <v>16</v>
       </c>
       <c r="D42" s="3">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="E42" s="6">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -3806,11 +3807,11 @@
         <v>9</v>
       </c>
       <c r="D43" s="3">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E43" s="6">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
@@ -3836,10 +3837,10 @@
         <v>21</v>
       </c>
       <c r="D44" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E44" s="6">
-        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="F44" s="3">
@@ -3866,11 +3867,11 @@
         <v>1</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E45" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -3896,10 +3897,10 @@
         <v>1</v>
       </c>
       <c r="D46" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E46" s="6">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F46" s="3">
@@ -3926,10 +3927,10 @@
         <v>5</v>
       </c>
       <c r="D47" s="3">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="E47" s="6">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F47" s="3">
@@ -3956,10 +3957,10 @@
         <v>2</v>
       </c>
       <c r="D48" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E48" s="6">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F48" s="3">
@@ -3986,11 +3987,11 @@
         <v>986</v>
       </c>
       <c r="D49" s="3">
-        <v>85</v>
+        <f t="shared" si="0"/>
+        <v>134</v>
       </c>
       <c r="E49" s="6">
-        <f t="shared" si="0"/>
-        <v>901</v>
+        <v>852</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -4016,16 +4017,16 @@
         <v>1</v>
       </c>
       <c r="D50" s="3">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E50" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="3">
         <v>1</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="7">
         <v>46024</v>
       </c>
       <c r="H50" s="2" t="s">
@@ -4046,10 +4047,10 @@
         <v>47</v>
       </c>
       <c r="D51" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E51" s="6">
-        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="F51" s="3">
@@ -4076,11 +4077,11 @@
         <v>0</v>
       </c>
       <c r="D52" s="3">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E52" s="6">
-        <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -4109,7 +4110,6 @@
         <v>0</v>
       </c>
       <c r="E53" s="6">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F53" s="3">
@@ -4136,16 +4136,16 @@
         <v>36</v>
       </c>
       <c r="D54" s="3">
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="E54" s="6">
-        <f t="shared" si="0"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F54" s="3">
         <v>15</v>
       </c>
-      <c r="G54" s="9">
+      <c r="G54" s="7">
         <v>46030</v>
       </c>
       <c r="H54" s="2" t="s">
@@ -4163,14 +4163,14 @@
         <v>94</v>
       </c>
       <c r="C55" s="3">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D55" s="3">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="E55" s="6">
-        <f t="shared" si="0"/>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F55" s="3">
         <v>10</v>
@@ -4196,17 +4196,17 @@
         <v>27</v>
       </c>
       <c r="D56" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E56" s="6">
-        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="F56" s="3">
-        <v>0</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>11</v>
+        <v>25</v>
+      </c>
+      <c r="G56" s="7">
+        <v>46038</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>11</v>
@@ -4226,16 +4226,16 @@
         <v>0</v>
       </c>
       <c r="D57" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E57" s="6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F57" s="3">
         <v>0</v>
       </c>
-      <c r="G57" s="9"/>
+      <c r="G57" s="7"/>
       <c r="H57" s="2" t="s">
         <v>98</v>
       </c>
@@ -4251,20 +4251,20 @@
         <v>99</v>
       </c>
       <c r="C58" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D58" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E58" s="6">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>2</v>
       </c>
-      <c r="E58" s="6">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>11</v>
+      <c r="G58" s="7">
+        <v>46024</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>100</v>
@@ -4281,14 +4281,14 @@
         <v>101</v>
       </c>
       <c r="C59" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E59" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="3">
         <v>0</v>
@@ -4326,17 +4326,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
